--- a/GUA/IPPU/A2_Extra_Inputs/A-Xtra_Emissions.xlsx
+++ b/GUA/IPPU/A2_Extra_Inputs/A-Xtra_Emissions.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\GUA_Modelos_Sectoriales_2024\M0_IPPU\A2_Extra_Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\0_guatemala_2025\IPPU_GUA_v1_2025\A2_Extra_Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4163A71-1118-4525-882D-AEAA6E2DB71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9758083-5AF7-409E-B32E-B74472B80310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GHGs" sheetId="1" r:id="rId1"/>
     <sheet name="Externalities" sheetId="2" r:id="rId2"/>
-    <sheet name="Other" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GHGs!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,32 +36,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Ignacio Alfaro</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{9D966BCA-1028-4D7D-8260-91432EF6166C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tengo muchas dudas acá que solo con Luis puedo aclarar</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
   <si>
     <t>External Cost</t>
   </si>
@@ -67,98 +45,113 @@
     <t>Tech</t>
   </si>
   <si>
-    <t>CO2e_sources</t>
-  </si>
-  <si>
-    <t>DIST_PCO</t>
-  </si>
-  <si>
     <t>EmissionActivityRatio</t>
   </si>
   <si>
     <t>Final Unit</t>
   </si>
   <si>
-    <t>Drop some references here</t>
-  </si>
-  <si>
     <t>Emission</t>
   </si>
   <si>
     <t>EmissionsPenalty</t>
   </si>
   <si>
-    <t>RAW_MAT_CLK</t>
-  </si>
-  <si>
-    <t>RAW_MAT_CEM</t>
-  </si>
-  <si>
     <t>PROD_CLK_TRAD</t>
   </si>
   <si>
-    <t>PROD_CEM</t>
-  </si>
-  <si>
-    <t>Mt CO2eq/Mt clinker</t>
-  </si>
-  <si>
-    <t>PROD_CAL</t>
-  </si>
-  <si>
-    <t>PROD_VID</t>
-  </si>
-  <si>
-    <t>CARBO_PROC</t>
-  </si>
-  <si>
-    <t>PROD_HIER</t>
+    <t>CO2e_IPPU</t>
+  </si>
+  <si>
+    <t>PARAFFIN</t>
+  </si>
+  <si>
+    <t>LUBRI_OILS</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC32</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC125</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC134a</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC143a</t>
+  </si>
+  <si>
+    <t>MtCO2e/Mt Cal</t>
+  </si>
+  <si>
+    <t>INGEI 2022</t>
   </si>
   <si>
     <t>PROD_FERRO</t>
   </si>
   <si>
-    <t>LUBRI</t>
-  </si>
-  <si>
-    <t>CERA_PAR</t>
-  </si>
-  <si>
-    <t>REFR_AC</t>
-  </si>
-  <si>
-    <t>CO2e_CEM</t>
-  </si>
-  <si>
-    <t>CO2e_CAL</t>
-  </si>
-  <si>
-    <t>CO2e_VID</t>
-  </si>
-  <si>
-    <t>CO2e_CARBONATO</t>
-  </si>
-  <si>
-    <t>CO2e_HIER</t>
-  </si>
-  <si>
-    <t>CO2e_FERRO</t>
-  </si>
-  <si>
-    <t>CO2e_LUB</t>
-  </si>
-  <si>
-    <t>CO2e_CERAS</t>
-  </si>
-  <si>
-    <t>CO2e_RAC</t>
+    <t>MtCO2e/Mt Clinker</t>
+  </si>
+  <si>
+    <t>MtCO2e/Mt FeNi</t>
+  </si>
+  <si>
+    <t>MtCO2e/Mt ceras</t>
+  </si>
+  <si>
+    <t>LIME_CAL_PROD</t>
+  </si>
+  <si>
+    <t>LIME_DOL_PROD</t>
+  </si>
+  <si>
+    <t>GLASS_PROD</t>
+  </si>
+  <si>
+    <t>CARBONATE_CERAMICS</t>
+  </si>
+  <si>
+    <t>CARBONATE_ASH</t>
+  </si>
+  <si>
+    <t>IRON_STEEL</t>
+  </si>
+  <si>
+    <t>MtCO2e/Mt lubricantes</t>
+  </si>
+  <si>
+    <t>MtCO2e/Mt Acero</t>
+  </si>
+  <si>
+    <t>MtCO2e/Mt Vidrio</t>
+  </si>
+  <si>
+    <t>CRT</t>
+  </si>
+  <si>
+    <t>MtCO2e/Mt carbonatos</t>
+  </si>
+  <si>
+    <t>MtCO2e/ktHFC32</t>
+  </si>
+  <si>
+    <t>MtCO2e/ktHFC125</t>
+  </si>
+  <si>
+    <t>MtCO2e/ktHFC134a</t>
+  </si>
+  <si>
+    <t>MtCO2e/ktHFC143a</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,20 +168,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,7 +189,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -211,17 +227,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -229,24 +245,38 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -257,99 +287,68 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{A5BE04F9-2BBD-4FEC-9AC3-2B0FFDA92B71}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFFCC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -624,240 +623,319 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="7" t="s">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0.5202</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.77</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.11550000000000001</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0.44</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0.41</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0.18</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="7" t="s">
+      <c r="B10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0.58960000000000001</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0.58960000000000001</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="7" t="s">
+      <c r="B12" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="11">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="11">
-        <v>0.52029999999999998</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="11">
+        <v>3.17</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="11">
+        <v>1.3</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="B15" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="9">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35B896B-BFBE-403F-A891-C25041EF70AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35B896B-BFBE-403F-A891-C25041EF70AE}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>5</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E14F0C-085B-4F8B-80A4-853CC51FC5EB}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>9.3399999999999997E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1084,27 +1162,50 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1C01EF8-DE2A-41D4-BC54-4A97649C7A61}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFFB2CC7-4028-40CF-B585-77900DA351B4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0d55314f-45f1-40c9-9fce-63556e193d03"/>
+    <ds:schemaRef ds:uri="48eed89a-7418-4977-ae3a-838f0fac8ec5"/>
+    <ds:schemaRef ds:uri="416d42ac-85ec-40c4-8054-6c816fd4b6a7"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35441C8A-19E3-4E1B-B1D1-A71AE4D2DAA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B2D6248-039D-405F-A1B4-BED39B1E804D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+    <ds:schemaRef ds:uri="081a93ea-d517-42a5-a2b7-457060aa7471"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B767FFCF-1C32-4046-8A73-811A25F365F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69F79AB8-49D9-484F-991A-27FAE0E62C64}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>